--- a/src/test/resources/testdata/LoginData.xlsx
+++ b/src/test/resources/testdata/LoginData.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SeleniumTestNG_Parallel\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A02B75F-4DCE-40DD-90B4-EB9240047275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14BB7942-72F7-47FB-BF34-5CEC6650C4C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3354A436-17E3-47D8-8548-6A8A1BAAD720}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="LoginData" sheetId="3" r:id="rId1"/>
+    <sheet name="LoginSuccess" sheetId="1" r:id="rId2"/>
+    <sheet name="LoginFail" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -25,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="15">
   <si>
     <t>admin</t>
   </si>
@@ -39,7 +41,37 @@
     <t>status</t>
   </si>
   <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>admin123@example.com</t>
+  </si>
+  <si>
+    <t>Success</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>role</t>
+  </si>
+  <si>
+    <t>anhtest@gmail.com</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
+    <t>project manager</t>
+  </si>
+  <si>
     <t>admin@example.com</t>
+  </si>
+  <si>
+    <t>employee@example.com</t>
+  </si>
+  <si>
+    <t>1234567</t>
   </si>
 </sst>
 </file>
@@ -65,12 +97,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="1">
@@ -86,9 +124,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -403,16 +465,71 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9855548-650E-431D-8B2D-53FEA4BA5E64}">
-  <dimension ref="A1:D2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF92B6D2-EF8D-4F64-A203-139A29B6AD13}">
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.77734375" customWidth="1"/>
+    <col min="2" max="2" width="21.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{807283AC-E3A9-462F-A1EA-6E4A1C8234A1}"/>
+    <hyperlink ref="A3" r:id="rId2" xr:uid="{3CFF19E0-36C9-4BE4-B55A-D80E19874234}"/>
+    <hyperlink ref="A4" r:id="rId3" xr:uid="{92E33E1A-73A2-4726-9250-441925B42D93}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId4"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9855548-650E-431D-8B2D-53FEA4BA5E64}">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="25.77734375" customWidth="1"/>
+    <col min="2" max="2" width="21.109375" customWidth="1"/>
+    <col min="3" max="3" width="21.88671875" customWidth="1"/>
+    <col min="4" max="4" width="12.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -425,15 +542,87 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>4</v>
+      <c r="A2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="4">
+        <v>123456</v>
+      </c>
+      <c r="C3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{B2BA2D34-84B5-4F4D-BB61-88373DB43279}"/>
+    <hyperlink ref="A3" r:id="rId2" xr:uid="{1EE9A3F9-DDE0-4830-8E1B-C8A021936AC3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0828104-8143-44DC-B5E7-CA59C32F0A46}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="26.6640625" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" customWidth="1"/>
+    <col min="3" max="3" width="20.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>